--- a/Configs/GameConfig/Datas/fg/#RaidUnit-突袭编成.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidUnit-突袭编成.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,17 +656,17 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>foundry.strider</t>
+          <t>silent.echo_hunter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>foundry</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>enemy_strider</t>
+          <t>enemy_echo_hunter</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -675,20 +675,20 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>flank</t>
+          <t>assassin,fast</t>
         </is>
       </c>
     </row>
@@ -696,17 +696,17 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>foundry.armorbot</t>
+          <t>silent.prism</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>foundry</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>enemy_armorbot</t>
+          <t>enemy_prism</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -715,20 +715,20 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>armored,heat_resistant</t>
+          <t>deflect</t>
         </is>
       </c>
     </row>
@@ -736,37 +736,117 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
+          <t>foundry.strider</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>enemy_strider</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>assault</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>22</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>55</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>flank</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>foundry.armorbot</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>enemy_armorbot</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>armored,heat_resistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>foundry.repairbot</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>foundry</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>enemy_repairbot</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>siege</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>20</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" t="n">
         <v>50</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>repair</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#RaidUnit-突袭编成.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidUnit-突袭编成.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,6 +852,126 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>foundry.minelayer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>enemy_minelayer</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sabotage</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>flank</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>foundry.loader</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>enemy_loader</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>foundry.siege_heavy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>enemy_siege_heavy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>80</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>160</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>armored,heat_resistant</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#RaidUnit-突袭编成.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidUnit-突袭编成.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,246 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>clarity.sprayer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>enemy_sprayer</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>insulated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>clarity.oil_crawler</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>enemy_oil_crawler</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>assault</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>clarity.corrosion_swarm</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>enemy_corrosion_swarm</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sabotage</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>swarm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>clarity.ln2_pump</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>enemy_ln2_pump</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>70</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cryo,insulated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>clarity.deact_drone</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>enemy_deact_drone</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sabotage</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>40</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>clarity.settling_tank</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>enemy_settling_tank</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>120</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>200</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>insulated</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
